--- a/artfynd/A 35197-2025 artfynd.xlsx
+++ b/artfynd/A 35197-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64935423</v>
+        <v>64935417</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>889</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Granåsen, intill NR, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>641997.9659008369</v>
+        <v>641961</v>
       </c>
       <c r="R2" t="n">
-        <v>6608559.411116118</v>
+        <v>6608564</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,24 +743,14 @@
           <t>2004-01-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2004-01-16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1 ex. på levande tall, omkr. 154 cm.</t>
+          <t>På grenar på äldre, levande tall, omkr. 148 cm.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,7 +774,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Levande tall. # Tall</t>
+          <t>Grenar på äldre, levande tall. # Tall</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -816,15 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64935417</v>
+        <v>64935421</v>
       </c>
       <c r="B3" t="n">
-        <v>88488</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,34 +803,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>889</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Irpicodon pendulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Granåsen, intill NR, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>641960.744634165</v>
+        <v>641949</v>
       </c>
       <c r="R3" t="n">
-        <v>6608563.576487709</v>
+        <v>6608484</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,24 +869,14 @@
           <t>2004-01-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2004-01-16</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På grenar på äldre, levande tall, omkr. 148 cm.</t>
+          <t>2 ex. på levande tall, omkr. 143 cm.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,7 +900,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Grenar på äldre, levande tall. # Tall</t>
+          <t>Levande tall. # Tall</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -948,15 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>64935421</v>
+        <v>64935422</v>
       </c>
       <c r="B4" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +948,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>641948.5440967684</v>
+        <v>642003</v>
       </c>
       <c r="R4" t="n">
-        <v>6608483.539195705</v>
+        <v>6608555</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1030,24 +995,14 @@
           <t>2004-01-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2004-01-16</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2 ex. på levande tall, omkr. 143 cm.</t>
+          <t>1 ex. på levande tall, omkr. 156 cm.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1089,15 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97865259</v>
+        <v>64935423</v>
       </c>
       <c r="B5" t="n">
-        <v>56632</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,21 +1055,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1127,9 +1077,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1138,13 +1088,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>641977.741650427</v>
+        <v>641998</v>
       </c>
       <c r="R5" t="n">
-        <v>6608583.987117274</v>
+        <v>6608559</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1168,27 +1118,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-05-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-01-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-05-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-01-16</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>1 sjungande.</t>
+          <t>1 ex. på levande tall, omkr. 154 cm.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1199,6 +1139,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre åstallskog.</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Levande tall. # Tall</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1212,6 +1167,117 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>97865259</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Granåsen, intill NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>641978</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6608584</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yttergran</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1 sjungande.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35197-2025 artfynd.xlsx
+++ b/artfynd/A 35197-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64935417</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64935421</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1041,6 +1056,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64935422</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1167,6 +1187,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64935423</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1278,8 +1303,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97865259</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>